--- a/InputData/ctrl-settings/BESHFoFRV/Boolean Elec Suppliers Have Foresight of Future RPS Values.xlsx
+++ b/InputData/ctrl-settings/BESHFoFRV/Boolean Elec Suppliers Have Foresight of Future RPS Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\eps-us-analysis\InputData\ctrl-settings\BESHFoFRV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\ctrl-settings\BESHFoFRV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44B0CC01-C3A0-4ACE-B858-7C66C9FC85C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3987D8DF-44E5-4C4D-96AD-E4F41610CCD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3870" yWindow="5955" windowWidth="24060" windowHeight="9165" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
